--- a/data/output/2025/evaluasi_97.xlsx
+++ b/data/output/2025/evaluasi_97.xlsx
@@ -1403,7 +1403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1645,20 +1645,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.077952690373273</v>
+        <v>-1.411434439283506</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1673,20 +1673,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.22992604922901</v>
+        <v>-3.416537007971036</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q4-25</t>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1701,18 +1701,578 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>-3.422690195424721</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>25.44221594499289</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-26.85813886966918</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>8.442284161973115</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5.231142351245813</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-3.647451900627583</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-7.513418309626796</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-6.13343105822584</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1089499390940002</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-6.847840582207409</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-8.282891190351437</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-6.279194562627756</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.2528126998957597</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1.18174564342098</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1.728185167296571</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_2025_prov vs implisit_y-on-y_pkrt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.6805438480291748</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-5.033861224188244</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-5.967379639789083</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>7.077952690373273</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.22992604922901</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>9702</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kabupaten Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>-2.121516911412874</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -1729,7 +2289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2167,18 +2727,354 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>3.490792294486751</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Yalimo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-6.817218938480423</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Yalimo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-6.87312105119284</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Yalimo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3.371975308147971</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Yalimo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-2.132203050638504</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Yalimo</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.4157177743564494</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Yalimo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1.616417711456783</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Yalimo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-2.06486026201562</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Yalimo</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.3529136645715399</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Yalimo</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.6615288518035229</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_2025_prov vs implisit_y-on-y_pkrt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Yalimo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.642550204860517</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Yalimo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.1153120358560514</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_2025_prov vs implisit_y-on-y_pmtb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>9706</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kabupaten Yalimo</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>6.592237028826956</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2195,7 +3091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2465,20 +3361,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.26006742361318</v>
+        <v>19.40000000000002</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2493,18 +3389,382 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>33.34000000000001</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10.13687527829997</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.592601165865137</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.58292113417455</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.46270137571631</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.4616445251822392</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.7355972226891022</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-2.822100000000021</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.312331728325797</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_2025_prov vs implisit_y-on-y_pkrt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-1.315200639817453</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-2.070395929682705</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-2.062511500992044</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.26006742361318</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9701</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Nduga</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>16.37343818137641</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2521,7 +3781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2679,20 +3939,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.55790886992691</v>
+        <v>7.63649570679995</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2707,18 +3967,578 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>32.17197700045379</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>18.5987406842344</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.949929361517351</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>9.16673580216704</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-5.293277080292478</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>24.46822802277143</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.717308907540516</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.841926328465488</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.393850728853413</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1084620653435121</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5031927868478168</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-2.836956523240873</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-5.716652269527709</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.07991257162310425</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q4-25_prov vs implisit_y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.6478082418186852</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_2025_prov vs implisit_y-on-y_pkrt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-2.072652484710078</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-1.553126095864464</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>6.044328413713732</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-2.102645113056189</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>14.55790886992691</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9707</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kabupaten Yahukimo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>12.85627907043663</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2735,7 +4555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2893,18 +4713,298 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>5.457973692451659</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9708</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Bintang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.873340429139395</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9708</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Bintang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-3.639605235175145</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9708</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Bintang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4.865633637281608</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9708</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Bintang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.769660192217566</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9708</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Bintang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5844735661435861</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9708</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Bintang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4456784187571166</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9708</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Bintang</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.299888363076382</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_2025_prov vs implisit_y-on-y_pkrt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9708</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Bintang</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2.772927279092477</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9708</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Bintang</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-3.440788911808963</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9708</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Pegunungan Bintang</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>4.082037449438204</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2921,7 +5021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3135,20 +5235,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.926185900548793</v>
+        <v>1.423999999999969</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q4-25</t>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3163,18 +5263,214 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>1.441820874440188</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9704</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tolikara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.009513493452244</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9704</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Tolikara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6965529502066019</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9704</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Tolikara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4728948027652761</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9704</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Tolikara</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3283768811531815</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9704</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Tolikara</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1000621704937365</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9704</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Tolikara</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2.926185900548793</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9704</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Tolikara</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>-4.831464476352324</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3191,7 +5487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3405,20 +5701,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-4.675018302758333</v>
+        <v>4.146249999999923</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3433,20 +5729,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.208085432229186</v>
+        <v>3.890323638558638</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q4-25</t>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3461,18 +5757,326 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>-7.522823529115004</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9703</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Lanny Jaya</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-6.352706817963965</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9703</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Lanny Jaya</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6.021385476440531</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9703</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Lanny Jaya</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-4.906420393936794</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9703</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Lanny Jaya</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4903725203030018</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>9703</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Lanny Jaya</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.6341426671131174</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9703</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Lanny Jaya</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.341582686014925</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_2025_prov vs implisit_y-on-y_pkrt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9703</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Lanny Jaya</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-3.248555196128877</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>9703</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Lanny Jaya</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.06537785999255689</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>9703</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Lanny Jaya</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-4.675018302758333</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>9703</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Lanny Jaya</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3.208085432229186</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9703</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Lanny Jaya</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>6.71608575719062</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3489,7 +6093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3580,6 +6184,314 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9705</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Tengah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.07251600421495204</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>9705</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Tengah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3294464383448485</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>9705</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Tengah</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.313087327330395</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>9705</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Tengah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1283272145491578</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>9705</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Tengah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.6575755348769532</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9705</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Tengah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.122471934429744</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9705</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Tengah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2991404015655059</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9705</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Tengah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.06158675733337193</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9705</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Tengah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.4556778972124996</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9705</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Tengah</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.2446941510528542</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9705</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamberamo Tengah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.1143445033183183</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
